--- a/branches/feature-s3-annotation-ig/ValueSet-vs-senologie-preop-markierung.xlsx
+++ b/branches/feature-s3-annotation-ig/ValueSet-vs-senologie-preop-markierung.xlsx
@@ -104,10 +104,22 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>markierung-draht</t>
-  </si>
-  <si>
-    <t>Drahtmarkierung (Wire guided)</t>
+    <t>712639003</t>
+  </si>
+  <si>
+    <t>Drahtmarkierung (Hook wire localisation)</t>
+  </si>
+  <si>
+    <t>77343006</t>
+  </si>
+  <si>
+    <t>Angiographische Markierung</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>markierung-clip</t>
@@ -116,19 +128,7 @@
     <t>Clip-Markierung</t>
   </si>
   <si>
-    <t>System URI</t>
-  </si>
-  <si>
     <t>https://www.senologie.org/fhir/CodeSystem/form-helper</t>
-  </si>
-  <si>
-    <t>77343006</t>
-  </si>
-  <si>
-    <t>Angiographische Markierung</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>Level</t>
@@ -568,14 +568,14 @@
         <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>13</v>
@@ -589,14 +589,14 @@
         <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
